--- a/wooclap/imports/optional/04_Search_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/04_Search_Part_2_optional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$3</definedName>

--- a/wooclap/imports/optional/04_Search_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/04_Search_Part_2_optional.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L01-O01 · An estimate must never be greater than the true remaining cost. The true cost is 5. Which estimate breaks this rule?</t>
+          <t>L01-O01 · A robot moves horizontally or vertically on a grid, one unit per move, and must avoid obstacles. Which proposed heuristic is guaranteed admissible for every reachable state?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0.</t>
+          <t>The length of any legal route already found from that state to the goal.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>Manhattan distance plus 1, to compensate for possible obstacles.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>5.</t>
+          <t>Twice Manhattan distance when the map contains many obstacles.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>7.</t>
+          <t>Manhattan distance to the goal with the obstacles ignored.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L01-O03 · Why can an estimate of the remaining distance help a search algorithm?</t>
+          <t>L01-O03 · An edge u→v costs 2. The heuristic values are h(u) = 5 and h(v) = 2; the current path to u has cost g = 3. After extending that path to v, how does its A* score f = g + h change, and is this edge consistent?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>It removes the need for a destination.</t>
+          <t>f rises from 8 to 9; the edge is consistent because the step costs 2.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Every estimate guarantees the shortest route.</t>
+          <t>f falls from 8 to 7; the edge is consistent because its cost is positive.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>It replaces the map with a list of correct answers.</t>
+          <t>f stays at 8; the increase in g always exactly cancels the change in h.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>It can help the algorithm choose promising places to explore first.</t>
+          <t>f falls from 8 to 7; the edge is inconsistent because 5 &gt; 2 + 2.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
